--- a/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_fea_001/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_fea_001/extracted.xlsx
@@ -284,6 +284,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -489,11 +494,6 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
-    <comment ref="G5" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
     <comment ref="H5" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -525,11 +525,6 @@
       </text>
     </comment>
     <comment ref="F6" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="G6" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1331,17 +1326,17 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>Lunar Orbiter Antenna Boom Root Bracket (BRK-2107)</t>
+          <t>Lunar Orbiter Antenna Boom Root Bracket BRK-2107</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>FE model BRK-ANL-012 used to certify bracket margins under limit/ultimate loads and verify first modal frequency ≥250 Hz for LO-1 flight hardware</t>
+          <t>Finite-element stress and modal analysis of BRK-2107 bracket for LO-1 flight design certification</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>Abaqus/Standard FE model of a machined 7050-T7451 aluminum boom root bracket that transfers bending and axial loads into the spacecraft primary deck via four M8 fasteners. The model is used to demonstrate yield/ultimate margins, verify that the first bending mode exceeds 250 Hz, screen for fatigue at fillet hot spots under random vibration, and support flight drawing release and qualification review board exit for the LO-1 lunar orbiter.</t>
+          <t>Abaqus/Standard 2023 HF6 linear-elastic FE model (BRK-ANL-012) of a machined 7050-T7451 aluminum bracket transferring boom loads to the spacecraft primary deck. Model supports: (1) margin-of-safety demonstration at limit and ultimate quasi-static loads per LV-ICD-LO1-D Rev D, (2) verification that first bending/torsional modes exceed 250 Hz, (3) fatigue screening under 14.1 Grms random vibration, and (4) selection of fillet radii and bolt preload. Results feed flight drawing release and QRB exit. Valid for temperatures −50 to +70 °C, fillet radius ≥3.0 mm, and torque 10–14 N·m per PROC-FAST-17.</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
@@ -1371,7 +1366,7 @@
       </c>
       <c r="I3" s="12" t="inlineStr">
         <is>
-          <t>S. Rao (primary); L. Cortez (checker/peer reviewer)</t>
+          <t>S. Rao (primary); L. Cortez (checker/peer review)</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -1379,9 +1374,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>report.md (Structural Model Credibility Assessment Report, Project BRK-2107, BRK-ANL-012, 2026-08-06, Space Systems Division Structures &amp; Dynamics Group)</t>
         </is>
       </c>
       <c r="L3" s="12" t="inlineStr">
@@ -1500,7 +1495,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Structural acceptance criteria per STR-STD-014 and LV-ICD-LO1-D</t>
+          <t>STR-STD-014 Structural Acceptance Criteria</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1510,7 +1505,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Bracket must achieve FoS ≥1.25 at limit load and ≥1.40 at ultimate load against yielding; first bending mode ≥250 Hz under qualification mass properties; pin displacement within pointing error budget (≤0.5 mm); bolt axial load below 75% of proof load.</t>
+          <t>Bracket must achieve FoS ≥1.25 at limit load and ≥1.4 at ultimate load against yielding; first structural mode must exceed 250 Hz under qualification mass properties; bolt axial load must remain below 75% of proof load at ultimate; pin displacement must remain within 0.5 mm to maintain antenna pointing error budget.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -1532,12 +1527,12 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>BRK-ANL-012 — Abaqus/Standard 2023 HF6 FE Model</t>
+          <t>BRK-ANL-012 Abaqus/Standard FE Model</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Nonlinear contact FE model of BRK-2107 bracket using C3D10 quadratic tetrahedra at filleted regions and C3D8R hexahedra on flats; includes pretensioned bolt shanks, finite-sliding contact, RBE3 deck stiffness, and Lanczos modal extraction up to 2 kHz.</t>
+          <t>Abaqus/Standard 2023 HF6 finite-element model of BRK-2107 using C3D10 quadratic tetrahedra and C3D8R hexahedra, nonlinear contact, pretensioned bolt elements, and RBE3 deck stiffness boundary; supports static, modal, and random-vibration screening analyses.</t>
         </is>
       </c>
     </row>
@@ -1549,12 +1544,12 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>DU-1 Static and Modal Test Data</t>
+          <t>DU-1 Component Static and Modal Test Data</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Six strain-gage measurements at fillet roots and web transitions under limit-load vector, plus tap-test and sine-sweep modal data measuring first mode at 312 Hz; used as primary validation comparator for strain (7.4% RMS error) and frequency (305 Hz predicted vs. 312 Hz measured).</t>
+          <t>Six strain-gage measurements at fillet roots and web transitions under limit-load envelope, plus tap-test and sine-sweep modal data (first mode 312 Hz) from development unit DU-1 on fixture FX-122.</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1561,12 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>MMPDS-2020 Material Properties and Vendor Certification Data</t>
+          <t>MMPDS-2020 Material Properties — 7050-T7451</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>A-basis yield (505 MPa) and ultimate (572 MPa) strengths, elastic modulus (72.4 GPa), Poisson's ratio (0.33), and CTE (23.2 μm/m-K) for 7050-T7451 plate; cross-checked against vendor certs with ≤1.1% delta.</t>
+          <t>A-basis yield (505 MPa) and ultimate (572 MPa) strengths, elastic modulus (72.4 GPa), and Poisson's ratio (0.33) for 7050-T7451 aluminum plate used as primary material inputs.</t>
         </is>
       </c>
     </row>
@@ -1583,12 +1578,12 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>ADAMS Boom Joint Load Envelope</t>
+          <t>LO1-MBD-214 Boom Joint Load Envelope</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Multibody dynamics-derived limit load envelope providing boom root moment (600 N·m), axial force (4.0 kN), and lateral shear (0.8 kN) used as boundary conditions in the FE model.</t>
+          <t>ADAMS multibody dynamics output providing limit-load moment (600 N·m), axial force (4.0 kN), and lateral shear (0.8 kN) applied at the boom pin bore as boundary conditions for the bracket FE model.</t>
         </is>
       </c>
     </row>
@@ -2025,7 +2020,7 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>Static strain-gage correlation — limit load, DU-1 development unit</t>
+          <t>Mesh Refinement and Hotspot Stress Convergence Study</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -2040,12 +2035,12 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Predicted strains at six fillet and web-transition gage locations under the 1.0x limit load vector compared to measurements from strain gages SG1–SG6 on fixture FX-122 replicating bolt pattern and deck thickness.</t>
+          <t>Three-level mesh refinement (0.8, 0.6, 0.4 mm target element size) at the critical boom-side lug fillet. Richardson-like extrapolation applied to nodal stresses using a 1/r structural stress method to obtain asymptotic hotspot stress estimate.</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>TEST-REP-BRK-DEV-01 measured strain values at six locations across six load cases</t>
+          <t>Richardson extrapolation asymptote; displacement convergence benchmark</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
@@ -2055,12 +2050,12 @@
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
-          <t>Mean absolute percentage error across gages and load cases; gage factor calibration applied</t>
+          <t>Richardson extrapolation / Grid Convergence Index (GCI)</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>7.4% RMS mean absolute percentage error across all gage/load-case combinations</t>
+          <t>Hotspot stress extrapolated to 317 ± 21 MPa (95% CI); GCI on hotspot stress 6.5%; GCI on tip displacement 2.7%; displacement numerical error &lt;3%</t>
         </is>
       </c>
       <c r="I3" s="12" t="inlineStr">
@@ -2072,7 +2067,7 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>Modal frequency correlation — first bending mode, sine sweep and tap test</t>
+          <t>Static Strain-Gage Correlation — DU-1 Component Test</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
@@ -2082,27 +2077,27 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>First bending mode frequency of the bracket/deck subassembly predicted by the FE model (post bolt shear-area update) compared to tap-test and electrodynamic shaker sine-sweep measurements of DU-1 hardware torqued to 10.5 N·m.</t>
+          <t>Predicted strains from limit-load FE analysis compared to six strain-gage measurements (SG1–SG6) at fillet roots and web transitions on development unit DU-1 tested on fixture FX-122 under the limit-case load vector.</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>TEST-REP-BRK-DEV-01 and CORR-BRK-012; measured first mode 312 Hz confirmed within 3 Hz by sine sweep</t>
+          <t>Measured strain-gage data from TEST-REP-BRK-DEV-01</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
-          <t>Point comparison; MAC = 0.91 for first mode shape</t>
+          <t>Mean absolute percentage error across six load cases; gage factor calibration applied</t>
         </is>
       </c>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>−2.2% frequency error (305 Hz predicted vs. 312 Hz measured); MAC = 0.91</t>
+          <t>Mean absolute percentage error 7.4% RMS across six load cases</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
@@ -2114,7 +2109,7 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Mesh refinement and GCI study — fillet hot-spot stress and tip displacement</t>
+          <t>Modal Frequency Correlation — Tap Test and Sine Sweep</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
@@ -2124,27 +2119,22 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Three mesh refinement levels at the boom-side lug fillet (0.8, 0.6, 0.4 mm target element size) with Richardson extrapolation and Grid Convergence Index computed for both tip displacement and hot-spot notch stress.</t>
+          <t>First bending mode frequency predicted by FE model (post bolt-stiffness update) compared to tap-test and electrodynamic shaker sine-sweep measurements on DU-1. Bolt effective shear-area factor updated from 0.5 to 0.58 based on supplier data for partial-thread engagement; change documented in commit 2f3c6e1 and CORR-BRK-012.</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>Richardson-extrapolated asymptotic value; structural stress method asymptote</t>
+          <t>Measured first mode 312 Hz from tap test and sine sweep (TEST-REP-BRK-DEV-01, CORR-BRK-012)</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G5" s="13" t="inlineStr">
-        <is>
-          <t>Richardson extrapolation; Grid Convergence Index (GCI); 95% confidence interval on extrapolated stress</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>GCI on critical notch stress 6.5%; extrapolated hot-spot stress 317 ± 21 MPa (95% CI); tip displacement GCI 2.7% (converged 0.236 mm)</t>
+          <t>Predicted 305 Hz vs. measured 312 Hz; error −2.2%; MAC = 0.91 for first mode shape</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
@@ -2156,7 +2146,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>Cross-code benchmark — independent Nastran SOL 106 reproduction</t>
+          <t>Cross-Code Independent Verification — MSC Nastran SOL 106</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
@@ -2166,12 +2156,12 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Independent analyst in Loads &amp; Dynamics team reproduced the baseline limit-load case using MSC Nastran SOL 106 with CTETRA10 elements and glued contact; peak fillet stress compared to Abaqus contact model result.</t>
+          <t>Independent analyst reproduced the baseline limit-load case in MSC Nastran SOL 106 using CTETRA10 elements with glued contact. Peak fillet stress compared between Abaqus contact model and Nastran. After enforcing frictionless contact in Abaqus to match Nastran simplification, difference was 2.1%.</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>Abaqus/Standard BRK-ANL-012 baseline peak fillet stress; COMP-BENCH-BRK-01</t>
+          <t>Abaqus/Standard BRK-ANL-012 peak fillet stress results; documented in COMP-BENCH-BRK-01</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
@@ -2179,14 +2169,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
-        <is>
-          <t>Direct percentage difference; frictionless contact sensitivity comparison</t>
-        </is>
-      </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>Initial difference 5.2%; after matching contact assumption (frictionless) difference 2.1%</t>
+          <t>Initial difference 5.2%; reduced to 2.1% after contact-condition alignment</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
@@ -2198,7 +2183,7 @@
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>Monte Carlo uncertainty propagation — peak notch stress and modal frequency</t>
+          <t>Monte Carlo Uncertainty Propagation</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
@@ -2208,12 +2193,12 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>200-sample Latin Hypercube Sampling over elastic modulus (±3%), friction coefficient (0.15–0.25), bolt preload (10–14 kN), and load amplitude (±5%) to characterize output distributions for peak notch stress and first modal frequency.</t>
+          <t>200-sample Latin Hypercube Sampling over elastic modulus (±3%, normal), friction coefficient (0.15–0.25, uniform), bolt preload (10–14 kN, triangular), and load amplitude (±5%, normal). Output distributions assessed for peak notch stress, first modal frequency, and slip initiation.</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>Structural acceptance thresholds: Sy = 505 MPa at limit load; first mode ≥250 Hz</t>
+          <t>Acceptance thresholds: Sy = 505 MPa, first mode ≥250 Hz</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
@@ -2223,12 +2208,12 @@
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
-          <t>Latin Hypercube Sampling (LHS, n=200, seed 14729); variance-based sensitivity indices; probability of exceedance</t>
+          <t>Latin Hypercube Sampling (200 samples); variance-based sensitivity indices (Sobol first-order)</t>
         </is>
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>P(stress &gt; Sy at limit load) ≈ 1×10⁻³; 95th-percentile notch stress 342 MPa; P(f1 &lt; 250 Hz) ≈ 0; peak stress mean 312 MPa, std 18 MPa</t>
+          <t>Peak stress mean 312 MPa, std 18 MPa; P(stress &gt; Sy) ~1e−3; P(f1 &lt; 250 Hz) ~0; 95th-percentile hotspot stress 342 MPa at limit load</t>
         </is>
       </c>
       <c r="I7" s="13" t="inlineStr">
@@ -2382,12 +2367,12 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>Commercial solver installed from verified media, organization-level acceptance problems run, relevant patch notes reviewed, input files linted, compute environment frozen and documented.</t>
+          <t>Commercial solver installed from checksum-verified media; relevant bug reports reviewed; automated input linting; compute environment frozen and version-controlled</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>Abaqus/Standard 2023 HF6 installed from checksum-verified media on RHEL 8.8 (report §4.4, §4.13). Three organization-level benchmark problems run on the compute server prior to analysis with errors vs. closed-form ≤2% (cylinder: 0.7%, Kt hole: 0.33%, Hertz contact: 1.8%). Vendor patch notes reviewed for C3D10/pretension defects — none relevant identified (HF3–HF6). Input files passed ANSLINT v2.1 automated lint checks. OS and library environment frozen under CM-IT-07 change control; conda environment hash recorded (9a7f). Random seeds logged for reproducibility. Limitation: no formal ISO 9001 certification document cited; evidence is practice-based rather than externally audited.</t>
+          <t>Abaqus/Standard 2023 HF6 installed from checksum-verified media on RHEL 8.8 with OS update lockdown (CM-IT-07). Vendor patch notes reviewed for C3D10 contact and pretension defects; no relevant defects identified (HF3–HF6). Input files passed automated linting via ANSLINT v2.1 checking duplicate BCs, unconnected nodes, and unit keywords. Random seeds recorded (14729) for reproducibility. Model and scripts in Git LFS repository STR-MDL-BRK tag v1.3, commit 2f3c6e1, with frozen conda environment (env hash 9a7f). One-click Makefile reproduces all runs.</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -2409,19 +2394,19 @@
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" s="14" t="n">
         <v>3</v>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Comparison of solver output to analytical solutions or established benchmarks; errors within accepted tolerances for the element types and physics used.</t>
+          <t>Simple acceptance problems against closed-form solutions run on the analysis compute server prior to analysis; errors within acceptable tolerance</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>Three benchmark problems (thick cylinder internal pressure, plate-with-hole tension, Hertzian line contact) run on the analysis server with closed-form comparisons; errors 0.7–1.8% (§4.4). Cross-code comparison to MSC Nastran SOL 106 shows 2.1% stress difference after contact-model alignment (COMP-BENCH-BRK-01, §4.18). No method-of-manufactured-solutions or formal numerical order-of-convergence study for the code itself; benchmarks are case-specific rather than a systematic code verification suite. Prior flight-bracket analyses (COM-BRK-08, NAV-BRK-03) corroborate solver behavior in similar configurations (§4.2).</t>
+          <t>Three organisation-level acceptance problems were re-run on the compute server before analysis: thick cylinder under internal pressure (radial displacement error 0.7%), flat plate with hole under tension (Kt = 2.99 vs. 3.00 exact), and Hertzian line contact (maximum contact pressure 1.8% high). Cross-code comparison with MSC Nastran SOL 106 (COMP-BENCH-BRK-01) further corroborates code correctness. Prior use on two flight brackets (2019, 2022) with successful correlation provides additional code-level confidence.</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -2450,12 +2435,12 @@
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>Mesh convergence study at critical location; GCI or equivalent metric reported; extrapolated value with uncertainty bounds used for margin assessment.</t>
+          <t>Mesh convergence study with at least three refinement levels; GCI or Richardson extrapolation reported for critical QoI; element quality metrics documented</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Three-level mesh refinement study at fillet root (0.8, 0.6, 0.4 mm) with Richardson extrapolation yielding asymptotic hot-spot stress 317 ± 21 MPa (95% CI) and GCI of 6.5% on critical stress (§4.5). Tip displacement GCI 2.7% with converged value 0.236 mm. Element quality checks: aspect ratios &lt;3, Jacobian &gt;0.6, warp &lt;5°. Structural stress (1/r) extrapolation method applied at notch root. Both nodal-averaging and linearized notch stress methods compared. Mesh quality histograms archived in appendix. Hotspot extrapolation is explicit and the quantified uncertainty is carried into margin reporting.</t>
+          <t>Three-level mesh refinement study at critical fillet (0.8, 0.6, 0.4 mm). Element aspect ratios &lt;3, Jacobian &gt;0.6, no warped tets beyond 5°. Richardson-like extrapolation gave asymptotic hotspot stress 317 ± 21 MPa (95% CI); GCI on hotspot stress 6.5%; GCI on tip displacement 2.7%; displacement numerical error &lt;3%. Structural stress (1/r) and linearised notch stress methods both applied. Sensitivity of modal frequency to RBE3 vs. RBE2 deck boundary confirmed (&lt;2% frequency, ~4% local stress). Mesh quality histograms documented in appendix.</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -2484,12 +2469,12 @@
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Residual convergence criteria stated and met; contact penetration bounded; energy checks confirm no spurious modes or hourglassing.</t>
+          <t>Residual convergence criteria documented; equilibrium and energy checks performed; solver parameter sensitivity assessed</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>Residual force norm converged to &lt;1×10⁻⁶ of reference load; out-of-balance forces &lt;0.1% of applied at final increment (§4.6). Contact penetration &lt;0.2 μm. Artificial strain energy &lt;0.4% of total — no hourglassing. Repeated runs with penalty vs. augmented-Lagrange contact enforcement show hotspot stress variation ±3%. Rigid-body check (preload off) yields expected mode reduction to 160 Hz, confirming contact constraint is active. Automatic incrementation capped at 0.2 load step; contact stabilization disabled. Comprehensive convergence monitoring across multiple metrics.</t>
+          <t>Residual force norm target &lt;1e−6 of reference force; out-of-balance forces below 0.1% of applied at final increment; contact penetration &lt;0.2 μm. Artificial strain energy &lt;0.4% of total; no hourglassing (quadratic tets and full-integration hexes). Rigid-body diagnostic: removing bolt preloads produced expected slip and mode reduction to 160 Hz. Contact enforcement sensitivity (penalty vs. augmented Lagrange) changed hotspot stress within ±3%, demonstrating solver robustness. Automatic incrementation capped at 0.2 load step with contact stabilisation off.</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -2518,12 +2503,12 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Independent review of model setup; structured checklist covering BCs, materials, solver controls, and post-processing; peer review documented and dispositioned.</t>
+          <t>Independent structured desk check; peer review by qualified checker; boundary condition and post-processing verification</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>Structured desk check following CHK-STR-Nonlin-2024 (61 items: BCs, materials, solver controls, post-processing) conducted by checker L. Cortez (MSME, PE-CA) (§4.15). Peer review PR-021 resulted in addition of friction sensitivity run and load-path pressure-map check. Independent Nastran reproduction by separate Loads &amp; Dynamics analyst (§4.18). Unit tests in toolchain trap contradictory unit inputs. Input files linted by ANSLINT v2.1 for duplicate BCs and unconnected nodes. Analysis plan (ANL-PLN-BRK-012 Rev B) pre-defined QoIs and acceptance thresholds. Analyst qualifications documented (S. Rao, PhD, 11 yr; both analysts completed 2023 nonlinear contact training).</t>
+          <t>Structured desk check using Group checklist CHK-STR-Nonlin-2024 (61 items covering BCs, materials, solver controls, post-processing). Independent checker L. Cortez (MSME, PE-CA) reviewed analysis. Peer review (PR-021) resulted in addition of friction sensitivity run and load-path engagement check via contact pressure maps. Independent Nastran reproduction by Loads &amp; Dynamics team (COMP-BENCH-BRK-01). Unit-test toolchain traps contradictory unit inputs. ANSLINT v2.1 automated linting of input files. Analysis plan (ANL-PLN-BRK-012 Rev B) defines QoIs and V&amp;V activities with traceability to CDR/PDR figures via commit IDs.</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -2552,12 +2537,12 @@
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Governing physics justified for the loading regime; constitutive model appropriate; simplifications documented with sensitivity evidence; known limitations explicitly stated.</t>
+          <t>Governing equations and physical idealizations justified; known limitations explicitly documented; sensitivity runs for key idealisation choices performed</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>Linear elasticity with small-strain kinematics justified for aluminum bracket under quasi-static loads well below yield at limit (§3.1). Nonlinear finite-sliding contact at bracket–deck and washer interfaces is physically motivated and verified against rigid-body checks. Machining residual stress omission justified by XRD coupon data and &lt;0.03 margin impact in sensitivity run (§4.3). Equivalent stiffness deck boundary shown adequate for bracket-level stress and local modes (RBE3 vs. RBE2 sensitivity: &lt;2% modal, ~4% local stress). Pin-hole idealization justified by steel bushing/sleeve geometry. CTE mismatch included; thermo-mechanical coupling omitted with &lt;5 K gradient justification. All simplifications documented with quantified sensitivity where feasible. Explicit out-of-scope list provided (crack initiation, fretting, &lt;−80 °C, progressive joint slip) (§4.12, §7).</t>
+          <t>Linear elasticity with small-strain kinematics justified for 7050-T7451 at limit load (margins well within yield); isotropic material assumption consistent with MMPDS plate data. Nonlinear finite-sliding contact with calibrated friction (μ = 0.20 ± 0.05). Pretensioned beam-shank bolts per VDI 2230. Machining residual stress neglect justified by XRD witness coupon data and sensitivity run (±30 MPa membrane changed critical margin by &lt;0.03). Deck equivalent-stiffness boundary justified; RBE3 vs. RBE2 sensitivity run performed. CTE mismatch thermal sensitivity included for bounding. Explicit out-of-scope items documented: stress corrosion cracking, fretting wear, temperatures below −80 °C, progressive joint slip. Prior lineage on COM-BRK-08 and NAV-BRK-03 with similar approach validated within 6–10%.</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -2586,12 +2571,12 @@
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Material properties from recognized standards or testing with traceability; boundary conditions from measured/documented sources; input uncertainties characterized and propagated.</t>
+          <t>Material properties from recognised standards with A-basis values; loads from verified source; geometric inputs from controlled CAD; input uncertainties characterised and propagated</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Material properties from MMPDS-2020 A-basis (Sy=505 MPa, Su=572 MPa, E=72.4 GPa); cross-checked against vendor certs (≤1.1% delta) (§4.7). Elastic modulus derated −3% from coupon means to reflect handbook basis. Friction coefficient μ=0.20±0.05 from in-house torque–tension tests at 23°C. Bolt preload 12 kN ±2 kN per PROC-FAST-17. Loads from ADAMS envelope LO1-MBD-214 Rev C and LV-ICD-LO1-D Rev D. Fastener geometry per ISO 965-1. Input uncertainties explicitly characterized and propagated via 200-sample LHS (E, μ, preload, load amplitude) with variance-based sensitivity indices ranking their relative importance (§4.10, §4.11). Unit consistency enforced by automated toolchain checks.</t>
+          <t>Material: MMPDS-2020 A-basis Sy = 505 MPa, Su = 572 MPa; E = 72.4 GPa cross-checked against vendor certs (delta &lt;1.1%); E derated −3% for coupon mean vs. handbook minima. Friction: μ = 0.20 ± 0.05 from in-house torque–tension tests at 23 °C. Fastener: M8 Class 12.9 per ISO 965-1; preload 12 kN ± 2 kN per PROC-FAST-17. Loads: LO1-MBD-214 Rev C (ADAMS); applied as force couple with documented components. Geometry: CAD Rev D via scripted mid-mesh workflow; parameters in meshing.yaml. Input uncertainty quantified and propagated through 200-sample LHS Monte Carlo (Section 4.10). Variance-based sensitivity indices identify dominant inputs (preload 0.36, fillet radius 0.29, friction 0.21, load 0.11).</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -2620,12 +2605,12 @@
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Test article is production-representative; sample characterization documented; sample size adequate for the comparison goals.</t>
+          <t>Test articles representative of flight configuration; sufficient number of specimens for statistical characterisation</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>A single development unit (DU-1) was tested on fixture FX-122 (§4.8, TEST-REP-BRK-DEV-01). The report does not describe whether DU-1 was manufactured to flight tolerances or characterize dimensional deviations from nominal. No coupon material testing is reported separately — material properties rely on MMPDS handbook values validated by vendor certs. Six strain gages were placed at fillet roots and web transitions; gage factor calibration is mentioned but calibration uncertainty is not quantified. A single specimen limits statistical characterization of part-to-part variability. Prior bracket programs (COM-BRK-08, NAV-BRK-03) provide indirect lineage evidence but are different geometries.</t>
+          <t>A single development unit (DU-1) was tested on fixture FX-122. No replicate specimens were tested; the report does not characterise unit-to-unit manufacturing variability in the test article population. The DU-1 represents the design geometry with production-representative bolt pattern and deck thickness, but one specimen limits statistical inference. Adequacy is partially compensated by the LHS Monte Carlo propagating manufacturing scatter analytically, but physical replicate testing was not performed.</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -2654,12 +2639,12 @@
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Load application verified; instrumentation calibrated; test environment controlled and documented; measurement uncertainty reported.</t>
+          <t>Calibrated instrumentation; controlled load application; measurement uncertainty reported; test procedure documented</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Static test on fixture FX-122 replicating bolt pattern and deck thickness; load vector matched the limit-case envelope direction (§4.8). Sine sweep on electrodynamic shaker confirmed modal frequency within 3 Hz of tap-test result. Gage factors calibrated (§4.8). Bolt torque documented as 10.5 N·m. Test report TEST-REP-BRK-DEV-01 is cited. However, the report does not explicitly state instrument calibration traceability (NIST or equivalent), environmental conditions during test (temperature, humidity), or measurement uncertainty budgets for load cell or strain gages. These gaps prevent a higher rating despite the overall adequacy of the test setup description.</t>
+          <t>Six strain gages (SG1–SG6) at fillet roots and web transitions with calibrated gage factors. Load vector matched limit-case envelope direction. Tap test and electrodynamic shaker sine sweep measured first mode at 312 Hz (confirmed within 3 Hz between methods). Bolt torque controlled to 10.5 N·m. Test reported in TEST-REP-BRK-DEV-01 with fixture drawings and gage placement maps in appendix. Explicit measurement uncertainty on strain gages and force application is not quantified beyond gage-factor calibration mention; modal frequency repeatability (±3 Hz) provides partial uncertainty bound.</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -2688,12 +2673,12 @@
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Model boundary conditions explicitly matched to test conditions; differences identified and their impact on comparison quantified.</t>
+          <t>Model inputs directly matched to test conditions; boundary condition equivalence demonstrated; input discrepancies identified and assessed</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>Load vector in the model matches the limit-case envelope direction used in the static test (§4.8). Bolt torque of 10.5 N·m in test is within the 10–14 N·m operational range; effective shear-area factor updated (0.5→0.58) to match test-observed modal frequency, with change documented in CORR-BRK-012 and commit 2f3c6e1 (§4.9). Fixture FX-122 replicates bolt pattern and deck thickness. No material tuning was performed. However, the report does not provide a formal input-parameter comparison table between test and model with propagated measurement uncertainties; differences in deck compliance representation (RBE3 vs. actual fixture stiffness) are acknowledged but their quantitative impact on strain comparisons is not explicitly bounded.</t>
+          <t>Fixture FX-122 replicates bolt pattern and deck thickness; load vector direction matched limit-case envelope. Bolt torque in test (10.5 N·m) corresponds to the nominal preload range. One documented discrepancy resolved: effective shear-area factor on bolt shank updated (0.5 → 0.58) based on supplier partial-thread data after modal test, changing predicted first mode from 298 to 305 Hz; static stress unchanged by &lt;1 MPa. Change documented in commit 2f3c6e1 and CORR-BRK-012. Friction coefficient measured at 23 °C; test temperature alignment confirmed. Explicit propagation of test boundary condition uncertainty into predicted response is not quantified beyond the Monte Carlo input ranges.</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -2722,12 +2707,12 @@
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Quantitative error metrics at multiple comparison points; uncertainty bands on both prediction and measurement; statistical validation metric reported.</t>
+          <t>Quantitative error metrics for multiple QoIs; uncertainty bands on predictions; comparison to acceptance thresholds; multiple load cases</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Strain correlation: 7.4% RMS MAPE across six gage locations and six load cases (§4.8, §5). Modal frequency: 305 Hz predicted vs. 312 Hz measured (−2.2% error); MAC=0.91 for first mode shape (§5.2). GCI on stress (6.5%) and displacement (2.7%) provide prediction uncertainty bounds; extrapolated hot-spot stress reported with 95% CI (317±21 MPa) (§4.5). Monte Carlo provides 95th-percentile output distribution (342 MPa) and probability of exceedance (~1×10⁻³) (§4.10). Cross-code comparison documents 2.1% stress difference after contact normalization (§4.18). Margins reported as ranges with uncertainty. Multiple QoIs addressed with quantitative comparison. Prior-program comparisons (6–10% strain, ≤5% modal) cited as supporting lineage (§4.2). Dashboard format highlights pass/fail vs. thresholds (§4.17).</t>
+          <t>Static strains: 7.4% RMS mean absolute error across six gages and six load cases vs. measured. Modal frequency: predicted 305 Hz vs. measured 312 Hz (−2.2% error); MAC = 0.91 for first mode shape. Cross-code Nastran comparison: 2.1% stress difference after contact alignment. Hotspot stress reported with 95% CI (317 ± 21 MPa). Monte Carlo yields 95th-percentile stress 342 MPa vs. Sy = 505 MPa (margin retained at P95). Displacement GCI 2.7%; hotspot GCI 6.5%. Acceptance thresholds from STR-STD-014 explicitly evaluated. Results communicated with pre/post-correlation comparison and pass/fail dashboard.</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -2756,12 +2741,12 @@
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>QoIs directly address the safety and performance requirements; QoIs are measurable both computationally and experimentally; mapping from QoIs to acceptance criteria is explicit.</t>
+          <t>QoIs directly address the safety and performance decisions; measurable both computationally and experimentally; mapped to acceptance criteria</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>Analysis plan ANL-PLN-BRK-012 Rev B explicitly maps required design questions to QoIs: peak fillet notch stress (vs. yield/ultimate FoS thresholds), first eigenfrequency of bracket/deck assembly (vs. 250 Hz requirement), pin tip displacement (vs. 0.5 mm pointing budget), and bolt axial load (vs. 75% proof) (§4.1). All four QoIs are measured experimentally (strain gages for stress, shaker/tap test for frequency) and extracted from the FE model, enabling direct comparison. Acceptance criteria sourced explicitly from STR-STD-014 and LV-ICD-LO1-D. Random-vibration RMS stress screening QoI is also defined though noted as for screening only. QoIs cover all decision-relevant structural behaviors within the stated scope.</t>
+          <t>ANL-PLN-BRK-012 Rev B explicitly maps decision questions to QoIs: peak notch stress at fillet (yield margin), first eigenfrequency of bracket/deck assembly (250 Hz requirement), pin displacement (0.5 mm pointing budget), and bolt axial load (preload adequacy). All four QoIs are measurable computationally and experimentally (strains via gages, frequency via tap/sweep, displacement via geometry). Random vibration RMS stress added for fatigue screening relevance. Sensitivity analysis identifies which input parameters govern each QoI, confirming relevance of the modelled physics to the decision.</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -2790,12 +2775,12 @@
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>Validation test geometry, loads, and boundary conditions match or bracket the intended flight use case; gaps between validation conditions and COU are identified and bounded.</t>
+          <t>Validation geometry, load conditions, boundary conditions, and physics regime match the COU; gaps between validation and COU envelope identified and assessed</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>Component-level static test on DU-1 with fixture FX-122 replicating bolt pattern and deck thickness under the limit-load vector covers the primary COU loading mode (§4.8). Modal correlation covers the dynamic COU requirement. Prior bracket programs (COM-BRK-08 2019, NAV-BRK-03 2022) in the same material system provide additional validation lineage for the modeling approach (§4.2). Gaps: (1) Test was conducted at room temperature; COU includes −50 to +70°C range — friction coefficient temperature dependence acknowledged as uncertain (§7). (2) Random vibration fatigue screening relies on PSD inputs with modal participation rather than a dedicated vibration test correlation. (3) Ultimate load was not applied in the static test (only 1.0x limit). (4) Single development-unit test limits coverage of manufacturing variability. These gaps are documented in §7 but not fully bounded quantitatively.</t>
+          <t>Validation test (DU-1 / FX-122) used the actual bracket geometry, production bolt pattern, and the limit-load vector from the flight envelope — strong geometric and loading relevance. Modal test conditions (torque, boundary constraints) matched the analysis setup. Gaps explicitly documented: (1) test was at room temperature only; flight envelope extends to −50 °C where friction and anti-seize behavior are uncertain; (2) only a single development unit tested, not a production-representative population; (3) detailed deck laminate not represented; (4) fatigue life validation not performed (screening only). These gaps are acknowledged in Section 7 and partially mitigated by the conservative input ranges in the Monte Carlo. Prior correlation on two similar brackets (2019, 2022) provides supplementary evidence but not direct COU geometry.</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -2980,7 +2965,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Model BRK-ANL-012 is accepted for use in LO-1 bracket design certification (drawing release and QRB exit) under the conditions documented in the report. All primary acceptance criteria are met: peak notch stress at limit load (317±21 MPa) gives yield FoS of 1.59 nominal against Sy=505 MPa (required ≥1.25); at ultimate (444±30 MPa) the nominal FoS against Su=572 MPa is 1.29 (required ≥1.40 against yield — met; local yielding at ultimate flagged as a limitation); first bending mode 305 Hz exceeds the 250 Hz requirement; pin displacement 0.236 mm is within the 0.5 mm budget; bolt loads are below 75% of proof. Validation evidence includes 7.4% RMS strain correlation and −2.2% modal frequency error vs. hardware test, cross-code agreement within 2.1%, quantified GCI (6.5% stress, 2.7% displacement), and Monte Carlo uncertainty propagation showing P(yield exceedance at limit) ≈1×10⁻³. The following conditions attach to the acceptance: (1) Any fillet radius reduction below 3.0 mm or deck configuration change requires additional mesh refinement and a prototype spot-check test. (2) If a future load update or geometry change moves operating conditions outside the validated domain, the Make-target workflow must be re-executed and the evidence matrix CREDMAP-BRK-01 updated. (3) A plasticity run is recommended before finalising any design revision that brings ultimate stress closer to the current boundary. (4) A cold-torque test is recommended to de-risk friction-coefficient uncertainty at −50°C for future configurations. Model scope exclusions (stress corrosion cracking, fretting wear, temperatures below −80°C, progressive joint slip) must be respected; these behaviours require separate analyses.</t>
+          <t>Model BRK-ANL-012 meets the high-assurance (CL-3) credibility standard required for LO-1 bracket design certification. All primary acceptance criteria from STR-STD-014 are satisfied with quantified margin: limit-load yield FoS 1.59 nominal (P95 hotspot 342 MPa vs. Sy 505 MPa); first bending mode 305 Hz exceeds the 250 Hz requirement (measured 312 Hz, −2.2% error); bolt loads well below 75% proof; pin displacement 0.236 mm within 0.5 mm budget. Strain-gage correlation achieved 7.4% RMS error across six load cases; modal MAC = 0.91. Numerical uncertainties (GCI 6.5% on hotspot stress, 2.7% on displacement) are small relative to margins. A 200-sample Monte Carlo with four uncertain inputs gives P(yield exceedance at limit) ~1e−3. Independent cross-code check (Nastran SOL 106) confirms results within 2.1%. All 13 credibility factors are assessed; no factor falls below achieved level 2. Accepted with the following conditions noted: (a) if fillet radius is reduced below 3.0 mm or loads change materially, the mesh refinement runs and margin checks must be repeated; (b) a plasticity run is recommended if ultimate-load margins tighten; (c) cold-torque testing at −50 °C is recommended to de-risk anti-seize friction uncertainty before final qualification; (d) any post-CDR geometry or load changes must be processed through the configured Make workflow and the living evidence matrix (CREDMAP-BRK-01) updated accordingly.</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -2990,7 +2975,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Structures &amp; Dynamics Group, Space Systems Division (S. Rao, primary analyst; L. Cortez, checker)</t>
+          <t>Structures &amp; Dynamics Group, Space Systems Division (S. Rao / L. Cortez)</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
